--- a/Data Files/10.5. Credit Transfer - Failed - Duplicate transaction.xlsx
+++ b/Data Files/10.5. Credit Transfer - Failed - Duplicate transaction.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chindy\Chindy\BIFAST\Revamp\Komi-API Now\Komi-API\Data Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chindy\Chindy\BIFAST\Revamp\Automation\Komi-API BIFAST 2.0\Komi-API Now\Komi-API\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30F9203-F431-49E7-9CEF-A116E8435B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368EA1EF-7BEF-4BE1-B569-1D9507DA9545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>CLRG</t>
   </si>
@@ -42,170 +42,179 @@
     <t>01</t>
   </si>
   <si>
-    <t>Authorization</t>
-  </si>
-  <si>
-    <t>Basic QWRtaW5pc3RyYXRvcjptYW5hZ2U=</t>
-  </si>
-  <si>
-    <t>Content_Type</t>
-  </si>
-  <si>
-    <t>application/json</t>
-  </si>
-  <si>
-    <t>requestID</t>
-  </si>
-  <si>
-    <t>requestDate</t>
-  </si>
-  <si>
-    <t>20230728APIBANK101000000121</t>
-  </si>
-  <si>
-    <t>2023-07-28T15:17:00.282</t>
-  </si>
-  <si>
-    <t>numberOfTrx</t>
-  </si>
-  <si>
-    <t>settlementMethod</t>
-  </si>
-  <si>
-    <t>endToEndID</t>
-  </si>
-  <si>
-    <t>20230728APIBANK1010O0100000121</t>
-  </si>
-  <si>
-    <t>transactionID</t>
-  </si>
-  <si>
-    <t>channelType</t>
-  </si>
-  <si>
-    <t>transactionPurpose</t>
-  </si>
-  <si>
-    <t>01001</t>
-  </si>
-  <si>
-    <t>settlementAmount</t>
-  </si>
-  <si>
-    <t>11000.00</t>
-  </si>
-  <si>
-    <t>settlementCurrency</t>
-  </si>
-  <si>
-    <t>settlementDate</t>
-  </si>
-  <si>
-    <t>chargeBearer</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>NUR SYIFAUN NAS</t>
-  </si>
-  <si>
-    <t>natID</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>accountID</t>
-  </si>
-  <si>
-    <t>1234567891011121</t>
-  </si>
-  <si>
-    <t>accountType</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>rsdntSts</t>
-  </si>
-  <si>
-    <t>twnNm</t>
-  </si>
-  <si>
-    <t>0300</t>
-  </si>
-  <si>
-    <t>originatingBIC</t>
-  </si>
-  <si>
-    <t>APIBANK1</t>
-  </si>
-  <si>
-    <t>receivingBIC</t>
-  </si>
-  <si>
-    <t>APIBANK4</t>
-  </si>
-  <si>
-    <t>0102030405060708</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>john.smith@example.com</t>
-  </si>
-  <si>
-    <t>paymentInfo</t>
-  </si>
-  <si>
-    <t>Payment for housing</t>
-  </si>
-  <si>
-    <t>oriEndToEndID</t>
-  </si>
-  <si>
-    <t>creditorname</t>
-  </si>
-  <si>
-    <t>creditornatID</t>
-  </si>
-  <si>
-    <t>creditoraccountID</t>
-  </si>
-  <si>
-    <t>creditoraccountType</t>
-  </si>
-  <si>
-    <t>creditorproxyType</t>
-  </si>
-  <si>
-    <t>creditorproxyValue</t>
-  </si>
-  <si>
-    <t>creditortype</t>
-  </si>
-  <si>
-    <t>creditorrsdntSts</t>
-  </si>
-  <si>
-    <t>creditortwnNm</t>
-  </si>
-  <si>
-    <t>20230726APIBANK15100100008109</t>
+    <t>AppHdrId</t>
+  </si>
+  <si>
+    <t>ToId</t>
+  </si>
+  <si>
+    <t>BizMsgIdr</t>
+  </si>
+  <si>
+    <t>MsgDefIdr</t>
+  </si>
+  <si>
+    <t>BizSvc</t>
+  </si>
+  <si>
+    <t>CreDt</t>
+  </si>
+  <si>
+    <t>GrpHdrCreDtTm</t>
+  </si>
+  <si>
+    <t>GrpHdrMsgId</t>
+  </si>
+  <si>
+    <t>GrpHdrNbOfTxs</t>
+  </si>
+  <si>
+    <t>SttlmInfSttlmMtd</t>
+  </si>
+  <si>
+    <t>PmtIdEndToEndId</t>
+  </si>
+  <si>
+    <t>PmtIdTxId</t>
+  </si>
+  <si>
+    <t>LclInstrmPrtry</t>
+  </si>
+  <si>
+    <t>CtgyPurpPrtry</t>
+  </si>
+  <si>
+    <t>ChrgBr</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Ccy</t>
+  </si>
+  <si>
+    <t>DbtrNm</t>
+  </si>
+  <si>
+    <t>OrgIdId</t>
+  </si>
+  <si>
+    <t>DbtrAcctId</t>
+  </si>
+  <si>
+    <t>TpPrtry</t>
+  </si>
+  <si>
+    <t>DbtrAgtId</t>
+  </si>
+  <si>
+    <t>CdtrAgtId</t>
+  </si>
+  <si>
+    <t>CdtrNm</t>
+  </si>
+  <si>
+    <t>PrvtIdId</t>
+  </si>
+  <si>
+    <t>CdtrAcctOthrId</t>
+  </si>
+  <si>
+    <t>CdtrAcctTpPrtry</t>
+  </si>
+  <si>
+    <t>RmtInfRmtInf</t>
+  </si>
+  <si>
+    <t>EnvlpRsdntSts</t>
+  </si>
+  <si>
+    <t>EnvlpTwnNm</t>
+  </si>
+  <si>
+    <t>CdtrTp</t>
+  </si>
+  <si>
+    <t>CdtrRsdntSts</t>
+  </si>
+  <si>
+    <t>CdtrTwnNm</t>
+  </si>
+  <si>
+    <t>FASTIDJA</t>
+  </si>
+  <si>
+    <t>PDJBIDJA</t>
+  </si>
+  <si>
+    <t>20250424PDJBIDJA010O25001123</t>
+  </si>
+  <si>
+    <t>pacs.008.001.08</t>
+  </si>
+  <si>
+    <t>CLEAR</t>
+  </si>
+  <si>
+    <t>2025-04-24T08:05:41Z</t>
+  </si>
+  <si>
+    <t>2025-04-24T15:05:41.911</t>
+  </si>
+  <si>
+    <t>20250424PDJBIDJA01000014682</t>
+  </si>
+  <si>
+    <t>20250424PDJBIDJA010O25001177</t>
+  </si>
+  <si>
+    <t>20250424PDJBIDJA01000015075</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>01099</t>
+  </si>
+  <si>
+    <t>11678.00</t>
+  </si>
+  <si>
+    <t>ANDRY SYAPUTRA</t>
+  </si>
+  <si>
+    <t>3273182301870001</t>
+  </si>
+  <si>
+    <t>0019845621100</t>
+  </si>
+  <si>
+    <t>BMRIIDJA</t>
+  </si>
+  <si>
+    <t>KU000022000462138</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>0019845621101</t>
+  </si>
+  <si>
+    <t>Test transfer</t>
+  </si>
+  <si>
+    <t>0191</t>
+  </si>
+  <si>
+    <t>0294</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,16 +222,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -235,8 +236,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -270,22 +277,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -598,233 +617,228 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAC831-256C-49B0-B0F6-AAF164E4E88A}">
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="2" width="10.33203125" customWidth="1"/>
     <col min="3" max="3" width="32.44140625" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" customWidth="1"/>
-    <col min="6" max="6" width="23.44140625" customWidth="1"/>
-    <col min="7" max="7" width="43" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="10" max="10" width="34.44140625" customWidth="1"/>
-    <col min="11" max="11" width="38.77734375" customWidth="1"/>
-    <col min="12" max="12" width="32.77734375" customWidth="1"/>
-    <col min="19" max="34" width="22.109375" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="22.44140625" customWidth="1"/>
+    <col min="8" max="8" width="29.109375" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" customWidth="1"/>
+    <col min="11" max="11" width="31.33203125" customWidth="1"/>
+    <col min="12" max="12" width="28.88671875" customWidth="1"/>
+    <col min="18" max="18" width="16.5546875" customWidth="1"/>
+    <col min="19" max="19" width="22.88671875" customWidth="1"/>
+    <col min="24" max="24" width="18.33203125" customWidth="1"/>
+    <col min="27" max="27" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="P1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="R1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="W1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Y1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="AA1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="AC1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="AD1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="AE1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="C2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="5">
+        <v>1</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="M2" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="N2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="O2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="Q2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="S2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="T2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="U2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="W2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AG1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="Y2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="Z2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="5">
-        <v>44895</v>
-      </c>
-      <c r="N2" t="s">
-        <v>2</v>
-      </c>
-      <c r="O2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S2" s="3" t="s">
+      <c r="AD2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="AF2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="U2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>400000001</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH2" s="3" t="s">
-        <v>16</v>
+      <c r="AG2" s="6" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="AC2" r:id="rId1" xr:uid="{A4F3BF85-2D71-F944-901B-78670569BC7B}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>